--- a/Docs/ISIS1225 - Tablas de Datos Lab 4 - Maquina 3 Andres Jose Velasco Mejia.xlsx
+++ b/Docs/ISIS1225 - Tablas de Datos Lab 4 - Maquina 3 Andres Jose Velasco Mejia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uniandes.sharepoint.com/sites/ISIS1225/Documentos compartidos/General/2025-10/Laboratorios/Lab 04 - Pilas y colas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\andre\Documents\lab 4\Laboratorio4-G07\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="120" documentId="13_ncr:1_{059725CA-9D74-4145-8FC3-28FE5756BBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CAB1D75-7132-4A69-A395-BC4C20E1FCBD}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1368B7E-CEF3-4083-BFBD-86BA20C50EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
+    <workbookView xWindow="2148" yWindow="420" windowWidth="17280" windowHeight="9420" xr2:uid="{D82936D8-D2C9-4EB2-9CBC-3665F65B95FD}"/>
   </bookViews>
   <sheets>
     <sheet name="01-Data Lab 4" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
   <si>
     <t>TIEMPOS PARA QUEUE [ms]</t>
   </si>
@@ -93,6 +93,108 @@
   </si>
   <si>
     <t xml:space="preserve">top(Linked List) </t>
+  </si>
+  <si>
+    <t>0.044</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>0.040</t>
+  </si>
+  <si>
+    <t>0.038</t>
+  </si>
+  <si>
+    <t>0.043</t>
+  </si>
+  <si>
+    <t>0.229</t>
+  </si>
+  <si>
+    <t>0.287</t>
+  </si>
+  <si>
+    <t>0.333</t>
+  </si>
+  <si>
+    <t>0.002</t>
+  </si>
+  <si>
+    <t>0.407</t>
+  </si>
+  <si>
+    <t>0.321</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>0.325</t>
+  </si>
+  <si>
+    <t>0.430</t>
+  </si>
+  <si>
+    <t>0.473</t>
+  </si>
+  <si>
+    <t>0.555</t>
+  </si>
+  <si>
+    <t>0.725</t>
+  </si>
+  <si>
+    <t>0.815</t>
+  </si>
+  <si>
+    <t>0.983</t>
+  </si>
+  <si>
+    <t>0.024</t>
+  </si>
+  <si>
+    <t>0.004</t>
+  </si>
+  <si>
+    <t>0.021</t>
+  </si>
+  <si>
+    <t>0.189</t>
+  </si>
+  <si>
+    <t>0.204</t>
+  </si>
+  <si>
+    <t>0.316</t>
+  </si>
+  <si>
+    <t>0.288</t>
+  </si>
+  <si>
+    <t>0.278</t>
+  </si>
+  <si>
+    <t>0.330</t>
+  </si>
+  <si>
+    <t>0.351</t>
+  </si>
+  <si>
+    <t>0.470</t>
+  </si>
+  <si>
+    <t>0.529</t>
+  </si>
+  <si>
+    <t>0.718</t>
+  </si>
+  <si>
+    <t>0.684</t>
+  </si>
+  <si>
+    <t>0.907</t>
   </si>
 </sst>
 </file>
@@ -178,7 +280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -199,6 +301,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -275,139 +380,6 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <name val="Dax-Regular"/>
-        <scheme val="none"/>
-      </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -571,6 +543,139 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <name val="Dax-Regular"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
@@ -688,7 +793,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -892,6 +997,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="#,##0">
+                  <c:v>1253</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="#,##0">
+                  <c:v>1253</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="#,##0">
+                  <c:v>2376</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="#,##0">
+                  <c:v>2810</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1029,6 +1158,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="#,##0">
+                  <c:v>1272</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="#,##0">
+                  <c:v>1719</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="#,##0">
+                  <c:v>2995</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="#,##0">
+                  <c:v>2915</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1330,6 +1483,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1337,7 +1491,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1370,7 +1523,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1569,6 +1722,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="#,##0">
+                  <c:v>1579</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="#,##0">
+                  <c:v>2332</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="#,##0">
+                  <c:v>5801</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="#,##0">
+                  <c:v>6174</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -1706,6 +1883,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="#,##0">
+                  <c:v>1184</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="#,##0">
+                  <c:v>1993</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="#,##0">
+                  <c:v>4053</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="#,##0">
+                  <c:v>5591</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2007,6 +2208,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2014,7 +2216,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2047,7 +2248,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2246,6 +2447,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2383,6 +2608,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -2684,6 +2933,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2691,7 +2941,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2724,7 +2973,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2928,6 +3177,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="#,##0">
+                  <c:v>1076</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="#,##0">
+                  <c:v>1552</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="#,##0">
+                  <c:v>3141</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="#,##0">
+                  <c:v>2896</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -3065,6 +3338,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="#,##0">
+                  <c:v>1090</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="#,##0">
+                  <c:v>1628</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="#,##0">
+                  <c:v>5682</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="#,##0">
+                  <c:v>3290</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -3366,6 +3663,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -3373,7 +3671,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3406,7 +3703,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3610,6 +3907,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="#,##0">
+                  <c:v>1201</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="#,##0">
+                  <c:v>1877</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="#,##0">
+                  <c:v>2966</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="#,##0">
+                  <c:v>3701</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -3747,6 +4068,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4" formatCode="#,##0">
+                  <c:v>1326</c:v>
+                </c:pt>
+                <c:pt idx="5" formatCode="#,##0">
+                  <c:v>2075</c:v>
+                </c:pt>
+                <c:pt idx="6" formatCode="#,##0">
+                  <c:v>3168</c:v>
+                </c:pt>
+                <c:pt idx="7" formatCode="#,##0">
+                  <c:v>3830</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -4048,6 +4393,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4055,7 +4401,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4088,7 +4433,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
+  <c:lang val="es-MX"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -4292,6 +4637,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -4429,6 +4798,30 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
@@ -4730,6 +5123,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4737,7 +5131,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -8378,19 +8771,19 @@
     <tableColumn id="2" xr3:uid="{23CECC62-35E0-466E-9502-4F5CC2E6F7A7}" name="Tamaño de la muestra (ARRAY_LIST)" dataDxfId="16">
       <calculatedColumnFormula>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{19B1D273-887B-4392-991E-015D36D99E5B}" name="enqueue (Array List) " dataDxfId="8"/>
-    <tableColumn id="4" xr3:uid="{56471E76-DCC6-4EED-8237-BCC256B57E91}" name="dequeue (Array List) " dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{61DF25D7-A2A3-4D39-B0C6-29804C1B33DB}" name="peek (Array List) " dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{092BA754-1EE8-42B8-A0C9-8E5FBAFE3FD2}" name="push (Array List)" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{F7FD567A-4A42-4CDC-9449-A0BA8E9714D3}" name="pop (Array List)" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{91D17C3E-2CFC-4978-91FF-19ADDF3A1CD9}" name="top(Array List) " dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{19B1D273-887B-4392-991E-015D36D99E5B}" name="enqueue (Array List) " dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{56471E76-DCC6-4EED-8237-BCC256B57E91}" name="dequeue (Array List) " dataDxfId="14"/>
+    <tableColumn id="5" xr3:uid="{61DF25D7-A2A3-4D39-B0C6-29804C1B33DB}" name="peek (Array List) " dataDxfId="13"/>
+    <tableColumn id="8" xr3:uid="{092BA754-1EE8-42B8-A0C9-8E5FBAFE3FD2}" name="push (Array List)" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{F7FD567A-4A42-4CDC-9449-A0BA8E9714D3}" name="pop (Array List)" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{91D17C3E-2CFC-4978-91FF-19ADDF3A1CD9}" name="top(Array List) " dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C35EFFA4-2B65-46C5-8257-6884800B9577}" name="Table13" displayName="Table13" ref="A13:H21" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C35EFFA4-2B65-46C5-8257-6884800B9577}" name="Table13" displayName="Table13" ref="A13:H21" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
   <autoFilter ref="A13:H21" xr:uid="{5C24B5A8-1B8E-4092-B34A-66FF5413D106}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -8402,13 +8795,13 @@
     <filterColumn colId="7" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{16584851-71BC-4FF5-B248-C3F46BA653AF}" name="Porcentaje de la muestra [pct]" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{4F9B7329-040C-4D35-96E7-B9181424DC65}" name="Tamaño de la muestra (LINKED_LIST)" dataDxfId="12">
+    <tableColumn id="1" xr3:uid="{16584851-71BC-4FF5-B248-C3F46BA653AF}" name="Porcentaje de la muestra [pct]" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{4F9B7329-040C-4D35-96E7-B9181424DC65}" name="Tamaño de la muestra (LINKED_LIST)" dataDxfId="6">
       <calculatedColumnFormula>Table13[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BDA028DF-4CED-4928-B040-96AD8F8A43EB}" name="enqueue (Linked List) " dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{A5E99D51-DD73-48A7-AE0D-601A8EE89AFA}" name="dequeue (Linked List)  " dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{EE99E4CD-A6F0-492B-B754-38221659D42F}" name="peek (Linked List)  " dataDxfId="9"/>
+    <tableColumn id="3" xr3:uid="{BDA028DF-4CED-4928-B040-96AD8F8A43EB}" name="enqueue (Linked List) " dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{A5E99D51-DD73-48A7-AE0D-601A8EE89AFA}" name="dequeue (Linked List)  " dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{EE99E4CD-A6F0-492B-B754-38221659D42F}" name="peek (Linked List)  " dataDxfId="3"/>
     <tableColumn id="8" xr3:uid="{D4319BDE-1663-4E02-A459-D4E464B40376}" name="push (Linked List) " dataDxfId="2"/>
     <tableColumn id="9" xr3:uid="{D1102AA4-3669-4976-AB80-8CA1D8EED93A}" name="pop (Linked List) " dataDxfId="1"/>
     <tableColumn id="11" xr3:uid="{A75BD949-6BC0-4683-B105-18DE72DE82D5}" name="top(Linked List) " dataDxfId="0"/>
@@ -8715,13 +9108,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B14742-4EBB-4241-AC8A-0E5F24F7BB7B}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="19.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="24.42578125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" style="6" customWidth="1"/>
-    <col min="6" max="12" width="24.42578125" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="24.44140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.44140625" style="6" customWidth="1"/>
+    <col min="6" max="12" width="24.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" customHeight="1">
@@ -8736,7 +9129,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="30">
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="27.6">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -8762,7 +9155,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="5" customFormat="1">
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="13.8">
       <c r="A3" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -8770,14 +9163,26 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>50</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="C3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" s="5" customFormat="1">
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="13.8">
       <c r="A4" s="2">
         <v>0.05</v>
       </c>
@@ -8785,12 +9190,24 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>500</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="C4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="2">
@@ -8800,12 +9217,24 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>1000</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="C5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2">
@@ -8815,12 +9244,24 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>2000</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="C6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="2">
@@ -8830,12 +9271,24 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>3000</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="C7" s="9">
+        <v>1253</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1579</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="9">
+        <v>1076</v>
+      </c>
+      <c r="G7" s="9">
+        <v>1201</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="2">
@@ -8845,12 +9298,24 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>5000</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="C8" s="9">
+        <v>1253</v>
+      </c>
+      <c r="D8" s="9">
+        <v>2332</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" s="9">
+        <v>1552</v>
+      </c>
+      <c r="G8" s="9">
+        <v>1877</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="2">
@@ -8860,12 +9325,24 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>8000</v>
       </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="C9" s="9">
+        <v>2376</v>
+      </c>
+      <c r="D9" s="9">
+        <v>5801</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="9">
+        <v>3141</v>
+      </c>
+      <c r="G9" s="9">
+        <v>2966</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="2">
@@ -8875,12 +9352,24 @@
         <f>Table1[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>10000</v>
       </c>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="C10" s="9">
+        <v>2810</v>
+      </c>
+      <c r="D10" s="9">
+        <v>6174</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="9">
+        <v>2896</v>
+      </c>
+      <c r="G10" s="9">
+        <v>3701</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="12" spans="1:8" ht="14.25" customHeight="1">
       <c r="C12" s="7" t="s">
@@ -8894,7 +9383,7 @@
       <c r="G12" s="8"/>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="1:8" s="5" customFormat="1" ht="30">
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="27.6">
       <c r="A13" s="4" t="s">
         <v>2</v>
       </c>
@@ -8920,7 +9409,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="5" customFormat="1">
+    <row r="14" spans="1:8" s="5" customFormat="1" ht="13.8">
       <c r="A14" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
@@ -8928,14 +9417,26 @@
         <f>Table13[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>50</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="C14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="15" spans="1:8" s="5" customFormat="1">
+    <row r="15" spans="1:8" s="5" customFormat="1" ht="13.8">
       <c r="A15" s="2">
         <v>0.05</v>
       </c>
@@ -8943,12 +9444,24 @@
         <f>Table13[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>500</v>
       </c>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="2">
@@ -8958,12 +9471,24 @@
         <f>Table13[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>1000</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="2">
@@ -8973,12 +9498,24 @@
         <f>Table13[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>2000</v>
       </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="C17" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="2">
@@ -8988,12 +9525,24 @@
         <f>Table13[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>3000</v>
       </c>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="C18" s="9">
+        <v>1272</v>
+      </c>
+      <c r="D18" s="9">
+        <v>1184</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="9">
+        <v>1090</v>
+      </c>
+      <c r="G18" s="9">
+        <v>1326</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="2">
@@ -9003,12 +9552,24 @@
         <f>Table13[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>5000</v>
       </c>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="C19" s="9">
+        <v>1719</v>
+      </c>
+      <c r="D19" s="9">
+        <v>1993</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F19" s="9">
+        <v>1628</v>
+      </c>
+      <c r="G19" s="9">
+        <v>2075</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="2">
@@ -9018,12 +9579,24 @@
         <f>Table13[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>8000</v>
       </c>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="C20" s="9">
+        <v>2995</v>
+      </c>
+      <c r="D20" s="9">
+        <v>4053</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="9">
+        <v>5682</v>
+      </c>
+      <c r="G20" s="9">
+        <v>3168</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="2">
@@ -9033,12 +9606,24 @@
         <f>Table13[[#This Row],[Porcentaje de la muestra '[pct']]]*10000</f>
         <v>10000</v>
       </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="C21" s="9">
+        <v>2915</v>
+      </c>
+      <c r="D21" s="9">
+        <v>5591</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="F21" s="9">
+        <v>3290</v>
+      </c>
+      <c r="G21" s="9">
+        <v>3830</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -9170,6 +9755,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010023858CF01A2EF24688B692775F4C60A4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="af74a0f8eb440a60883e9dd833f0742f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="164883f8-7691-4ecf-b54a-664c0d0edefe" xmlns:ns3="85e30bcc-d76c-4413-8e4d-2dce22fb0743" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f5ceeff32ffca1089660572a8ebd1782" ns2:_="" ns3:_="">
     <xsd:import namespace="164883f8-7691-4ecf-b54a-664c0d0edefe"/>
@@ -9418,15 +10012,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97C5E1E0-C817-4769-9D2D-1DC296B681FA}">
   <ds:schemaRefs>
@@ -9445,6 +10030,14 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24D72429-8592-4E2D-9A60-DFD77A3B0B84}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9461,12 +10054,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8DF3742-38F2-4B99-B335-CC4F04ED9F45}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>